--- a/ig/DM-JUILLET-2026/ValueSet-JDV-J105-EnsembleDiplome-RASS.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-JDV-J105-EnsembleDiplome-RASS.xlsx
@@ -49,7 +49,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -76,7 +76,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1516,7 +1516,7 @@
     <t>DIP322</t>
   </si>
   <si>
-    <t>Master en Psychologie ou Psychanalyse</t>
+    <t>Master en Psychologie ou Psychanalyse + formation établissement agréé incluant un stage en ESSMS</t>
   </si>
   <si>
     <t>DIP323</t>
